--- a/Configs/GameConfig/Datas/fg/#RaidStory-剧情突袭.xlsx
+++ b/Configs/GameConfig/Datas/fg/#RaidStory-剧情突袭.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,6 +535,32 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>raid.story.foundry_core.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>silent_mind_retaliation</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>silent_mind</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>raid.story.silent_mind.name</t>
         </is>
       </c>
     </row>
